--- a/artfynd/A 31062-2025 artfynd.xlsx
+++ b/artfynd/A 31062-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126212304</v>
       </c>
       <c r="B2" t="n">
-        <v>98258</v>
+        <v>98260</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126209994</v>
       </c>
       <c r="B3" t="n">
-        <v>98258</v>
+        <v>98260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126212064</v>
       </c>
       <c r="B4" t="n">
-        <v>98258</v>
+        <v>98260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126210408</v>
+        <v>126210457</v>
       </c>
       <c r="B5" t="n">
-        <v>98258</v>
+        <v>98364</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126210457</v>
+        <v>126210408</v>
       </c>
       <c r="B6" t="n">
-        <v>98362</v>
+        <v>98260</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,7 +1163,7 @@
         <v>126210310</v>
       </c>
       <c r="B7" t="n">
-        <v>98258</v>
+        <v>98260</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126212328</v>
       </c>
       <c r="B8" t="n">
-        <v>98258</v>
+        <v>98260</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 31062-2025 artfynd.xlsx
+++ b/artfynd/A 31062-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126212304</v>
       </c>
       <c r="B2" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126209994</v>
       </c>
       <c r="B3" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126212064</v>
       </c>
       <c r="B4" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126210457</v>
+        <v>126210408</v>
       </c>
       <c r="B5" t="n">
-        <v>98364</v>
+        <v>98262</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126210408</v>
+        <v>126210457</v>
       </c>
       <c r="B6" t="n">
-        <v>98260</v>
+        <v>98366</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,7 +1163,7 @@
         <v>126210310</v>
       </c>
       <c r="B7" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126212328</v>
       </c>
       <c r="B8" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 31062-2025 artfynd.xlsx
+++ b/artfynd/A 31062-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126212304</v>
       </c>
       <c r="B2" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126209994</v>
       </c>
       <c r="B3" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126212064</v>
       </c>
       <c r="B4" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126210408</v>
       </c>
       <c r="B5" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126210457</v>
       </c>
       <c r="B6" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126210310</v>
       </c>
       <c r="B7" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126212328</v>
       </c>
       <c r="B8" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 31062-2025 artfynd.xlsx
+++ b/artfynd/A 31062-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126212304</v>
       </c>
       <c r="B2" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126209994</v>
       </c>
       <c r="B3" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126212064</v>
       </c>
       <c r="B4" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126210408</v>
       </c>
       <c r="B5" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126210457</v>
       </c>
       <c r="B6" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126210310</v>
       </c>
       <c r="B7" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126212328</v>
       </c>
       <c r="B8" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 31062-2025 artfynd.xlsx
+++ b/artfynd/A 31062-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126212304</v>
       </c>
       <c r="B2" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126209994</v>
       </c>
       <c r="B3" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126212064</v>
       </c>
       <c r="B4" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126210408</v>
       </c>
       <c r="B5" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126210457</v>
       </c>
       <c r="B6" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126210310</v>
       </c>
       <c r="B7" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126212328</v>
       </c>
       <c r="B8" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 31062-2025 artfynd.xlsx
+++ b/artfynd/A 31062-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126212304</v>
+        <v>126212017</v>
       </c>
       <c r="B2" t="n">
-        <v>98278</v>
+        <v>99026</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>219788</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488898</v>
+        <v>488896</v>
       </c>
       <c r="R2" t="n">
-        <v>6824659</v>
+        <v>6824577</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126209994</v>
+        <v>126209838</v>
       </c>
       <c r="B3" t="n">
-        <v>98278</v>
+        <v>99035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489084</v>
+        <v>489121</v>
       </c>
       <c r="R3" t="n">
-        <v>6824835</v>
+        <v>6824814</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126212064</v>
+        <v>126209860</v>
       </c>
       <c r="B4" t="n">
-        <v>98278</v>
+        <v>99035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488879</v>
+        <v>489106</v>
       </c>
       <c r="R4" t="n">
-        <v>6824583</v>
+        <v>6824810</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126210408</v>
+        <v>126209994</v>
       </c>
       <c r="B5" t="n">
-        <v>98278</v>
+        <v>99035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489085</v>
+        <v>489084</v>
       </c>
       <c r="R5" t="n">
-        <v>6824723</v>
+        <v>6824835</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126210457</v>
+        <v>126210310</v>
       </c>
       <c r="B6" t="n">
-        <v>98382</v>
+        <v>99035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489085</v>
+        <v>489102</v>
       </c>
       <c r="R6" t="n">
-        <v>6824723</v>
+        <v>6824737</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126210310</v>
+        <v>126210408</v>
       </c>
       <c r="B7" t="n">
-        <v>98278</v>
+        <v>99035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489102</v>
+        <v>489085</v>
       </c>
       <c r="R7" t="n">
-        <v>6824737</v>
+        <v>6824723</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126212328</v>
+        <v>126212064</v>
       </c>
       <c r="B8" t="n">
-        <v>98278</v>
+        <v>99035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488895</v>
+        <v>488879</v>
       </c>
       <c r="R8" t="n">
-        <v>6824661</v>
+        <v>6824583</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1351,6 +1351,394 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126212304</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Tjädermyråsen, Tjädermyråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>488898</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6824659</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126212328</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Tjädermyråsen, Tjädermyråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>488895</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6824661</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126211958</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Tjädermyråsen, Tjädermyråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>488919</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6824579</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126210457</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Tjädermyråsen, Tjädermyråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>489085</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6824723</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31062-2025 artfynd.xlsx
+++ b/artfynd/A 31062-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126212017</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126209838</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126209860</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126209994</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126210310</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126210408</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126212064</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126212304</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126212328</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126211958</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,8 +1794,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126210457</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>